--- a/erp-server/erp-server-file/src/main/resources/excel/scm/contractInfoExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/contractInfoExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>合同编码</t>
   </si>
   <si>
+    <t>模板名称</t>
+  </si>
+  <si>
     <t>供应商名称</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.name}</t>
   </si>
   <si>
     <t>{.serviceProviderName}</t>
@@ -1057,30 +1063,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="24.75" customWidth="1"/>
-    <col min="2" max="2" width="37.125" customWidth="1"/>
-    <col min="3" max="3" width="24.75" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="15.125" customWidth="1"/>
-    <col min="8" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="17.375" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="37.125" customWidth="1"/>
+    <col min="4" max="4" width="24.75" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:12">
+    <row r="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1110,43 +1117,49 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
